--- a/data/trans_bre/POLIPATOLOGIA_5-Edad-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_5-Edad-trans_bre.xlsx
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,71</t>
+          <t>-0,43; 0,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,66</t>
+          <t>0,52; 5,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,21</t>
+          <t>0,69; 3,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,37</t>
+          <t>0,17; 2,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,19</t>
+          <t>0,36; 2,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,73</t>
+          <t>0,5; 3,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,19; —</t>
+          <t>-6,73; —</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 2,49</t>
+          <t>0,15; 2,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,18</t>
+          <t>1,46; 4,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,21</t>
+          <t>0,96; 3,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 3,16</t>
+          <t>-1,21; 3,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,51; 867,62</t>
+          <t>1,22; 773,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>138,05; 2870,03</t>
+          <t>142,04; 3139,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,09; —</t>
+          <t>16,26; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 149,81</t>
+          <t>-27,24; 147,09</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,71</t>
+          <t>0,77; 5,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,98</t>
+          <t>2,03; 7,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,91</t>
+          <t>2,07; 6,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,24; 13,52</t>
+          <t>5,02; 12,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,9; 503,67</t>
+          <t>19,82; 463,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,82; 545,82</t>
+          <t>57,39; 541,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,62; 439,09</t>
+          <t>50,19; 384,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>73,88; 528,12</t>
+          <t>68,27; 524,11</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 8,07</t>
+          <t>0,15; 8,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,36; 15,68</t>
+          <t>7,25; 15,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,51; 15,09</t>
+          <t>6,66; 14,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,88; 11,71</t>
+          <t>4,58; 11,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,74; 188,65</t>
+          <t>-0,41; 166,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>127,13; 568,93</t>
+          <t>119,34; 542,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,09; 424,52</t>
+          <t>89,5; 398,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,98; 124,85</t>
+          <t>34,08; 121,58</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 9,7</t>
+          <t>-0,7; 9,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 11,83</t>
+          <t>0,06; 12,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,51; 20,42</t>
+          <t>10,2; 21,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,12; 66,08</t>
+          <t>11,84; 63,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 94,84</t>
+          <t>-4,67; 102,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 110,86</t>
+          <t>0,29; 110,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>89,07; 326,77</t>
+          <t>90,44; 338,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>77,94; 510,94</t>
+          <t>71,7; 517,57</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 12,59</t>
+          <t>-1,01; 12,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,95; 22,19</t>
+          <t>7,51; 22,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,13; 16,44</t>
+          <t>3,76; 16,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,6; 20,02</t>
+          <t>8,87; 20,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 97,25</t>
+          <t>-7,2; 101,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,14; 134,43</t>
+          <t>29,85; 139,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,18; 107,0</t>
+          <t>16,7; 108,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,05; 67,64</t>
+          <t>23,27; 69,58</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,48</t>
+          <t>2,34; 4,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,85; 7,27</t>
+          <t>4,95; 7,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,12; 7,58</t>
+          <t>5,17; 7,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,47; 27,74</t>
+          <t>7,48; 27,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>59,86; 150,39</t>
+          <t>60,5; 149,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>110,47; 214,81</t>
+          <t>115,67; 227,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>127,29; 242,88</t>
+          <t>126,79; 243,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>86,67; 371,67</t>
+          <t>88,56; 365,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/POLIPATOLOGIA_5-Edad-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_5-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4823,48%</t>
+          <t>341,4%</t>
         </is>
       </c>
     </row>
@@ -670,12 +670,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,73</t>
+          <t>-0,17; 4,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>2,28</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>341,78%</t>
+          <t>423,35%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,06</t>
+          <t>0,65; 3,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,44</t>
+          <t>0,3; 2,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,36</t>
+          <t>0,48; 2,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,98</t>
+          <t>0,81; 4,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,73; —</t>
+          <t>10,79; —</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>1,73</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>56,89%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,6</t>
+          <t>0,02; 2,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,25</t>
+          <t>1,38; 4,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,41</t>
+          <t>0,98; 3,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 3,17</t>
+          <t>-0,48; 3,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 773,74</t>
+          <t>-19,93; 687,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>142,04; 3139,73</t>
+          <t>92,34; 2840,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,26; —</t>
+          <t>38,51; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 147,09</t>
+          <t>-13,19; 185,11</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,37</t>
+          <t>6,37</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>175,89%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,36</t>
+          <t>0,56; 5,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,21</t>
+          <t>2,28; 7,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,85</t>
+          <t>1,97; 6,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 12,63</t>
+          <t>3,65; 9,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,82; 463,18</t>
+          <t>6,51; 423,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,39; 541,15</t>
+          <t>64,42; 547,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,19; 384,78</t>
+          <t>42,58; 394,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>68,27; 524,11</t>
+          <t>42,4; 174,66</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,05</t>
+          <t>8,15</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>74,76%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 8,11</t>
+          <t>0,29; 8,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 15,27</t>
+          <t>7,48; 15,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,66; 14,35</t>
+          <t>6,57; 14,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 11,51</t>
+          <t>4,44; 11,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 166,68</t>
+          <t>2,2; 178,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>119,34; 542,85</t>
+          <t>126,12; 538,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,5; 398,7</t>
+          <t>90,77; 386,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,08; 121,58</t>
+          <t>33,36; 123,85</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37,54</t>
+          <t>15,0</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>247,25%</t>
+          <t>104,35%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 9,75</t>
+          <t>-0,4; 10,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,06; 12,46</t>
+          <t>-0,29; 12,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,2; 21,09</t>
+          <t>9,33; 20,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,84; 63,65</t>
+          <t>10,63; 19,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 102,59</t>
+          <t>-4,09; 106,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 110,01</t>
+          <t>-2,31; 108,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90,44; 338,87</t>
+          <t>81,76; 310,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>71,7; 517,57</t>
+          <t>63,5; 160,22</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14,51</t>
+          <t>14,6</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>44,05%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 12,83</t>
+          <t>-0,71; 12,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,51; 22,1</t>
+          <t>8,02; 22,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,76; 16,91</t>
+          <t>2,67; 16,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,87; 20,47</t>
+          <t>8,99; 19,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 101,07</t>
+          <t>-3,83; 91,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,85; 139,14</t>
+          <t>32,54; 137,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,7; 108,68</t>
+          <t>12,23; 109,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,27; 69,58</t>
+          <t>23,8; 66,75</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12,74</t>
+          <t>7,99</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>160,16%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,31</t>
+          <t>2,25; 4,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,95; 7,34</t>
+          <t>4,83; 7,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,62</t>
+          <t>5,05; 7,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,48; 27,48</t>
+          <t>6,67; 9,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>60,5; 149,69</t>
+          <t>56,27; 145,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>115,67; 227,23</t>
+          <t>110,21; 221,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>126,79; 243,91</t>
+          <t>128,79; 250,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>88,56; 365,95</t>
+          <t>73,23; 120,11</t>
         </is>
       </c>
     </row>
